--- a/templates/highschool_checklist.xlsx
+++ b/templates/highschool_checklist.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -487,6 +487,8 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -553,6 +555,16 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>신세계 이마트배 출전</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>대통령배 출전</t>
         </is>
       </c>
     </row>
@@ -579,6 +591,8 @@
         <v/>
       </c>
       <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -603,6 +617,8 @@
         <v/>
       </c>
       <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -627,6 +643,8 @@
         <v/>
       </c>
       <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -651,6 +669,8 @@
         <v/>
       </c>
       <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -675,6 +695,8 @@
         <v/>
       </c>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -699,6 +721,8 @@
         <v/>
       </c>
       <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -723,6 +747,8 @@
         <v/>
       </c>
       <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -747,6 +773,8 @@
         <v/>
       </c>
       <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -771,6 +799,8 @@
         <v/>
       </c>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -795,6 +825,8 @@
         <v/>
       </c>
       <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -819,6 +851,8 @@
         <v/>
       </c>
       <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -843,6 +877,8 @@
         <v/>
       </c>
       <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -867,6 +903,8 @@
         <v/>
       </c>
       <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -891,6 +929,8 @@
         <v/>
       </c>
       <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -915,6 +955,8 @@
         <v/>
       </c>
       <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -939,6 +981,8 @@
         <v/>
       </c>
       <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -963,6 +1007,8 @@
         <v/>
       </c>
       <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -987,6 +1033,8 @@
         <v/>
       </c>
       <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1011,6 +1059,8 @@
         <v/>
       </c>
       <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1035,6 +1085,8 @@
         <v/>
       </c>
       <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1059,6 +1111,8 @@
         <v/>
       </c>
       <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1083,6 +1137,8 @@
         <v/>
       </c>
       <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1107,6 +1163,8 @@
         <v/>
       </c>
       <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1131,6 +1189,8 @@
         <v/>
       </c>
       <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1155,6 +1215,8 @@
         <v/>
       </c>
       <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1179,6 +1241,8 @@
         <v/>
       </c>
       <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1203,6 +1267,8 @@
         <v/>
       </c>
       <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1227,6 +1293,8 @@
         <v/>
       </c>
       <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1251,6 +1319,8 @@
         <v/>
       </c>
       <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -1275,6 +1345,8 @@
         <v/>
       </c>
       <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1299,6 +1371,8 @@
         <v/>
       </c>
       <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -1323,6 +1397,8 @@
         <v/>
       </c>
       <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1347,6 +1423,8 @@
         <v/>
       </c>
       <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -1371,6 +1449,8 @@
         <v/>
       </c>
       <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1395,6 +1475,8 @@
         <v/>
       </c>
       <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -1419,6 +1501,8 @@
         <v/>
       </c>
       <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1443,6 +1527,8 @@
         <v/>
       </c>
       <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -1467,6 +1553,8 @@
         <v/>
       </c>
       <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -1491,6 +1579,8 @@
         <v/>
       </c>
       <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -1515,6 +1605,8 @@
         <v/>
       </c>
       <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -1539,6 +1631,8 @@
         <v/>
       </c>
       <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -1563,6 +1657,8 @@
         <v/>
       </c>
       <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -1587,6 +1683,8 @@
         <v/>
       </c>
       <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1611,6 +1709,8 @@
         <v/>
       </c>
       <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -1635,6 +1735,8 @@
         <v/>
       </c>
       <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -1659,6 +1761,8 @@
         <v/>
       </c>
       <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -1683,6 +1787,8 @@
         <v/>
       </c>
       <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -1707,6 +1813,8 @@
         <v/>
       </c>
       <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -1731,6 +1839,8 @@
         <v/>
       </c>
       <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -1755,6 +1865,8 @@
         <v/>
       </c>
       <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -1779,6 +1891,8 @@
         <v/>
       </c>
       <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -1803,6 +1917,8 @@
         <v/>
       </c>
       <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -1827,6 +1943,8 @@
         <v/>
       </c>
       <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -1851,6 +1969,8 @@
         <v/>
       </c>
       <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -1875,6 +1995,8 @@
         <v/>
       </c>
       <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -1899,6 +2021,8 @@
         <v/>
       </c>
       <c r="M57" s="2" t="n"/>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -1923,6 +2047,8 @@
         <v/>
       </c>
       <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -1947,6 +2073,8 @@
         <v/>
       </c>
       <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -1971,6 +2099,8 @@
         <v/>
       </c>
       <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:K60">
@@ -1983,7 +2113,7 @@
       <formula>AND(ISNUMBER(L2),L2&lt;=6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="C2:C60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="입력 오류" error="0~200 사이 정수를 입력하세요." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>200</formula2>
@@ -2000,6 +2130,9 @@
     <dataValidation sqref="J2:J60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="0~30 사이 정수" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>30</formula2>
+    </dataValidation>
+    <dataValidation sqref="N2:O60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"O,X"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2062,7 +2195,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>1. KBSA 홈페이지에서 2026 시즌 주말리그·황금사자기·청룡기·봉황대기에 출전한 경기도 소재 학교를 한 줄씩 적는다.</t>
+          <t>1. KBSA 홈페이지에서 2026 시즌 주말리그·신세계 이마트배·황금사자기·청룡기·대통령배·봉황대기에 출전한 경기도 소재 학교를 한 줄씩 적는다.</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2209,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>3. 주말리그 기록 유무, 세 전국대회 출전 여부(O/X), 경기 기록이 3주 이상 끊기지 않고 이어지는 구간 수를 적는다.</t>
+          <t>3. 주말리그 기록 유무, 전국대회 출전 여부(O/X, 이마트배·대통령배는 맨 오른쪽 두 열), 경기 기록이 3주 이상 끊기지 않고 이어지는 구간 수를 적는다.</t>
         </is>
       </c>
     </row>
